--- a/site/Log-Insights/headings.xlsx
+++ b/site/Log-Insights/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,51 +771,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Truncating Logs</t>
+          <t>Using Log Management Tab</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KF0N8XSHSYMA75XFSR3SX5WM</t>
+          <t>h_01KJ7GNM48P49Y7FKQW31G2NMH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KF0N8XSHSYMA75XFSR3SX5WM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KJ7GNM48P49Y7FKQW31G2NMH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Reporting Tab</t>
+          <t>Truncating Logs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KFAQG5EJW9VA1CY16X2MQ7C5</t>
+          <t>h_01KF0N8XSHSYMA75XFSR3SX5WM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFAQG5EJW9VA1CY16X2MQ7C5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KF0N8XSHSYMA75XFSR3SX5WM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Reporting Tab</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KFAQG5EN985AZG1KVQY4CPDC</t>
+          <t>h_01KFAQG5EJW9VA1CY16X2MQ7C5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFAQG5EN985AZG1KVQY4CPDC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFAQG5EJW9VA1CY16X2MQ7C5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>When Reports Are Created</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KFAQG5EQKRMTPQJ29WNASNHQ</t>
+          <t>h_01KFAQG5EN985AZG1KVQY4CPDC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFAQG5EQKRMTPQJ29WNASNHQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFAQG5EN985AZG1KVQY4CPDC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Report Definitions</t>
+          <t>When Reports Are Created</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KFAQG5EYDEFZP6SP65CZMHF8</t>
+          <t>h_01KFAQG5EQKRMTPQJ29WNASNHQ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFAQG5EYDEFZP6SP65CZMHF8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFAQG5EQKRMTPQJ29WNASNHQ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Report Definition</t>
+          <t>Report Definitions</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KFD28CDEMJZ0A87968V31QNS</t>
+          <t>h_01KFAQG5EYDEFZP6SP65CZMHF8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFD28CDEMJZ0A87968V31QNS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFAQG5EYDEFZP6SP65CZMHF8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Creating the Report Definition</t>
+          <t>Report Definition</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KFD2X3WPKHE6MZR7CZ7QEZGG</t>
+          <t>h_01KFD28CDEMJZ0A87968V31QNS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFD2X3WPKHE6MZR7CZ7QEZGG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFD28CDEMJZ0A87968V31QNS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perform the following steps:</t>
+          <t>Creating the Report Definition</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KFD2X3WQB3QMFHCNVRMDD86Q</t>
+          <t>h_01KFD2X3WPKHE6MZR7CZ7QEZGG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFD2X3WQB3QMFHCNVRMDD86Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFD2X3WPKHE6MZR7CZ7QEZGG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Relationship Between Reports and Report Definitions</t>
+          <t>Perform the following steps:</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KFFMQGFP0DD8RPJ5TZ90AT3B</t>
+          <t>h_01KFD2X3WQB3QMFHCNVRMDD86Q</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFFMQGFP0DD8RPJ5TZ90AT3B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFD2X3WQB3QMFHCNVRMDD86Q</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scheduling Behavior</t>
+          <t>Relationship Between Reports and Report Definitions</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,32 +979,54 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KFFMQGFQ4AJ9PYWCF23QG6Y3</t>
+          <t>h_01KFFMQGFP0DD8RPJ5TZ90AT3B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFFMQGFQ4AJ9PYWCF23QG6Y3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFFMQGFP0DD8RPJ5TZ90AT3B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Scheduling Behavior</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KFFMQGFQ4AJ9PYWCF23QG6Y3</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFFMQGFQ4AJ9PYWCF23QG6Y3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Time Range Selector in Log Insights</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>h_01KFDH63NZ034FVRT7ZRZATJZQ</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Log-Insights/#h_01KFDH63NZ034FVRT7ZRZATJZQ</t>
         </is>

--- a/site/Log-Insights/headings.xlsx
+++ b/site/Log-Insights/headings.xlsx
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Creating a Dashboard</t>
+          <t>Creating Dashboard</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Updating a Dashboard (Edit Mode)</t>
+          <t>Updating Dashboard (Edit Mode)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Edit Dashboard</t>
+          <t>Editing  Dashboard</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
